--- a/Statistical_documentation_in_R/main_results/saturated_models.xlsx
+++ b/Statistical_documentation_in_R/main_results/saturated_models.xlsx
@@ -2401,22 +2401,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.522532811872055</v>
+        <v>-0.503946176716643</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0565111250736306</v>
+        <v>0.0576967756870042</v>
       </c>
       <c r="D2" t="n">
-        <v>-9.24654766988315</v>
+        <v>-8.73439062609792</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00000684087098752106</v>
+        <v>0.0000230842042934912</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.650369858235153</v>
+        <v>-0.636995180038822</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.394695765508956</v>
+        <v>-0.370897173394465</v>
       </c>
     </row>
     <row r="3">
@@ -2424,22 +2424,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.588814749530602</v>
+        <v>-0.575214185091174</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0691262258397232</v>
+        <v>0.0688147154075705</v>
       </c>
       <c r="D3" t="n">
-        <v>-8.51796467083035</v>
+        <v>-8.35888344061789</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000013363747018288</v>
+        <v>0.0000317975072158554</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.745189136451138</v>
+        <v>-0.733901203383929</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.432440362610066</v>
+        <v>-0.416527166798418</v>
       </c>
     </row>
     <row r="4">
@@ -2447,22 +2447,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.75002240261201</v>
+        <v>-1.78201274145107</v>
       </c>
       <c r="C4" t="n">
-        <v>0.101601966008007</v>
+        <v>0.1066149052213</v>
       </c>
       <c r="D4" t="n">
-        <v>-17.2242966486898</v>
+        <v>-16.7144803791941</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0000000337668605127042</v>
+        <v>0.000000166082238424151</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.97986201777141</v>
+        <v>-2.02786715376579</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.52018278745262</v>
+        <v>-1.53615832913635</v>
       </c>
     </row>
     <row r="5">
@@ -2470,22 +2470,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.5039661484504</v>
+        <v>-1.53077579845466</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0914451365193512</v>
+        <v>0.102203062300632</v>
       </c>
       <c r="D5" t="n">
-        <v>-16.446649933451</v>
+        <v>-14.9777879840025</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0000000505834441382581</v>
+        <v>0.000000389795619605741</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.71082941903071</v>
+        <v>-1.76645648275045</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.29710287787009</v>
+        <v>-1.29509511415888</v>
       </c>
     </row>
     <row r="6">
@@ -2493,22 +2493,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.917611501199394</v>
+        <v>-0.944731756786608</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0508952818546215</v>
+        <v>0.054810292421479</v>
       </c>
       <c r="D6" t="n">
-        <v>-18.0294020931151</v>
+        <v>-17.2363932949277</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0000000226207741426975</v>
+        <v>0.00000013064545416219</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.03274462759946</v>
+        <v>-1.07112451776229</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.802478374799329</v>
+        <v>-0.818338995810928</v>
       </c>
     </row>
     <row r="7">
@@ -2516,22 +2516,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.08507924850189</v>
+        <v>-1.0754358809321</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0725733639480838</v>
+        <v>0.0725662391405374</v>
       </c>
       <c r="D7" t="n">
-        <v>-14.9514806737926</v>
+        <v>-14.8200581106225</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00000011602926458403</v>
+        <v>0.000000423123206021077</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.24925160358541</v>
+        <v>-1.24277392846639</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.920906893418374</v>
+        <v>-0.908097833397803</v>
       </c>
     </row>
     <row r="8">
@@ -2539,22 +2539,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.03204201943513</v>
+        <v>-1.02976256997693</v>
       </c>
       <c r="C8" t="n">
-        <v>0.112608890060802</v>
+        <v>0.128539338040889</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.16483608778925</v>
+        <v>-8.01126398868921</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00000735822616853887</v>
+        <v>0.0000432281503267705</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.28678102668093</v>
+        <v>-1.32617481503562</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.777303012189331</v>
+        <v>-0.733350324918229</v>
       </c>
     </row>
     <row r="9">
@@ -2562,22 +2562,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.42585548921212</v>
+        <v>-1.4068736130427</v>
       </c>
       <c r="C9" t="n">
-        <v>0.136395407746401</v>
+        <v>0.133034929578183</v>
       </c>
       <c r="D9" t="n">
-        <v>-10.4538379463861</v>
+        <v>-10.5752197374291</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00000247005498284997</v>
+        <v>0.00000558237511693736</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.73440333781843</v>
+        <v>-1.71365271077658</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.11730764060582</v>
+        <v>-1.10009451530881</v>
       </c>
     </row>
     <row r="10">
@@ -2585,22 +2585,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.71207985277415</v>
+        <v>-1.62158572100424</v>
       </c>
       <c r="C10" t="n">
-        <v>0.202795545409515</v>
+        <v>0.208046073389787</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.4423937878757</v>
+        <v>-7.79435869460558</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0000143625686936993</v>
+        <v>0.0000526457971858483</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.17083524840585</v>
+        <v>-2.10134082655407</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.25332445714245</v>
+        <v>-1.1418306154544</v>
       </c>
     </row>
     <row r="11">
@@ -2608,22 +2608,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.561163844775794</v>
+        <v>-0.536876107949066</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0510285206173355</v>
+        <v>0.0575486367539535</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.9970627795381</v>
+        <v>-9.32908472262261</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00000161356219803778</v>
+        <v>0.0000142205514383877</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.676598378197296</v>
+        <v>-0.669583502279045</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.445729311354293</v>
+        <v>-0.404168713619087</v>
       </c>
     </row>
     <row r="12">
@@ -2631,22 +2631,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.602699350697834</v>
+        <v>-0.58310538686948</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0598033417494486</v>
+        <v>0.0587635362310041</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.0780212788592</v>
+        <v>-9.92291179647948</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0000033539647059007</v>
+        <v>0.00000899277822499477</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.737983908595617</v>
+        <v>-0.718614344417395</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.46741479280005</v>
+        <v>-0.447596429321564</v>
       </c>
     </row>
     <row r="13">
@@ -2654,22 +2654,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.747230266770373</v>
+        <v>-0.719334442257415</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0492228750029985</v>
+        <v>0.0422525461555415</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.1805490176032</v>
+        <v>-17.0246412987605</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000000101671646867016</v>
+        <v>0.000000143884964331902</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.858580146031926</v>
+        <v>-0.816768988414999</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.635880387508819</v>
+        <v>-0.621899896099832</v>
       </c>
     </row>
     <row r="14">
@@ -2677,22 +2677,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.00784479539697</v>
+        <v>-1.02112971915193</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0792205035546168</v>
+        <v>0.0788926118034798</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.7220195552296</v>
+        <v>-12.9432870304199</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000000467394774562056</v>
+        <v>0.0000012019897107447</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.18705402495353</v>
+        <v>-1.20305640820781</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.828635565840412</v>
+        <v>-0.839203030096049</v>
       </c>
     </row>
     <row r="15">
@@ -2700,22 +2700,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.842595639332725</v>
+        <v>-0.810694155017496</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0767253043897403</v>
+        <v>0.0844182887270715</v>
       </c>
       <c r="D15" t="n">
-        <v>-10.9819784494123</v>
+        <v>-9.60330003417281</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0000016323457784762</v>
+        <v>0.0000114736653996938</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.01616033622585</v>
+        <v>-1.00536307790898</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.669030942439601</v>
+        <v>-0.61602523212601</v>
       </c>
     </row>
     <row r="16">
@@ -2723,22 +2723,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.38771533973957</v>
+        <v>-1.38952873893522</v>
       </c>
       <c r="C16" t="n">
-        <v>0.119423450039328</v>
+        <v>0.13043525273014</v>
       </c>
       <c r="D16" t="n">
-        <v>-11.6201243498037</v>
+        <v>-10.6530152688863</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00000101223460628985</v>
+        <v>0.0000052829338152939</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.65786995265211</v>
+        <v>-1.69031297110733</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.11756072682703</v>
+        <v>-1.08874450676312</v>
       </c>
     </row>
     <row r="17">
@@ -2746,22 +2746,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>-2.13346995869502</v>
+        <v>-2.16534802677748</v>
       </c>
       <c r="C17" t="n">
-        <v>0.283974708065115</v>
+        <v>0.34294762410445</v>
       </c>
       <c r="D17" t="n">
-        <v>-7.51288723292153</v>
+        <v>-6.31393214177214</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0000364317808259695</v>
+        <v>0.000229321197144213</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.77586537859805</v>
+        <v>-2.95618666612079</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.49107453879199</v>
+        <v>-1.37450938743417</v>
       </c>
     </row>
     <row r="18">
@@ -2769,22 +2769,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.589716508086025</v>
+        <v>-0.57671863357525</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0788416671128028</v>
+        <v>0.090740906332097</v>
       </c>
       <c r="D18" t="n">
-        <v>-7.47975695696905</v>
+        <v>-6.3556631390098</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0000377209222834836</v>
+        <v>0.000219276026761861</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.768068750072204</v>
+        <v>-0.78596753880924</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.411364266099847</v>
+        <v>-0.367469728341261</v>
       </c>
     </row>
     <row r="19">
@@ -2792,22 +2792,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.517079079002839</v>
+        <v>-0.526990102834865</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0575011322331576</v>
+        <v>0.0665104959441302</v>
       </c>
       <c r="D19" t="n">
-        <v>-8.99250256336116</v>
+        <v>-7.92341261862706</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00000859645528136521</v>
+        <v>0.000046796125826874</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.647155677153083</v>
+        <v>-0.68036358151651</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.387002480852594</v>
+        <v>-0.373616624153221</v>
       </c>
     </row>
     <row r="20">
@@ -2815,22 +2815,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.531183699583427</v>
+        <v>-0.526672293693725</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0272485547303722</v>
+        <v>0.02751511162932</v>
       </c>
       <c r="D20" t="n">
-        <v>-19.4940137133714</v>
+        <v>-19.1412014164793</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0000000113806270137953</v>
+        <v>0.0000000575026314200732</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.592824212842638</v>
+        <v>-0.590122254891541</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.469543186324217</v>
+        <v>-0.463222332495909</v>
       </c>
     </row>
     <row r="21">
@@ -2838,22 +2838,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.5092784317056</v>
+        <v>-1.52529419380527</v>
       </c>
       <c r="C21" t="n">
-        <v>0.136619689477489</v>
+        <v>0.136481760859964</v>
       </c>
       <c r="D21" t="n">
-        <v>-11.0472980686601</v>
+        <v>-11.1758097506544</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00000155270705386953</v>
+        <v>0.00000368018231463867</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.81833364083637</v>
+        <v>-1.84002169872829</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.20022322257483</v>
+        <v>-1.21056668888224</v>
       </c>
     </row>
     <row r="22">
@@ -2861,22 +2861,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.902145238457262</v>
+        <v>-0.835847001506377</v>
       </c>
       <c r="C22" t="n">
-        <v>0.356153753291663</v>
+        <v>0.425353850700325</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.53302184834333</v>
+        <v>-1.96506273572038</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0320759388524333</v>
+        <v>0.0849901566201877</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.70782100252346</v>
+        <v>-1.81671474014634</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0964694743910623</v>
+        <v>0.145020737133588</v>
       </c>
     </row>
     <row r="23">
@@ -2884,22 +2884,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.59475808947119</v>
+        <v>-1.59785071885406</v>
       </c>
       <c r="C23" t="n">
-        <v>0.138497835702315</v>
+        <v>0.137277397949917</v>
       </c>
       <c r="D23" t="n">
-        <v>-11.514678777356</v>
+        <v>-11.6395760898455</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00000109362484183233</v>
+        <v>0.00000270382841401389</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.90806196053723</v>
+        <v>-1.91441296619663</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.28145421840515</v>
+        <v>-1.28128847151148</v>
       </c>
     </row>
     <row r="24">
@@ -2907,22 +2907,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.40384996280401</v>
+        <v>-1.39653251395366</v>
       </c>
       <c r="C24" t="n">
-        <v>0.119581275169382</v>
+        <v>0.111146558116392</v>
       </c>
       <c r="D24" t="n">
-        <v>-11.7397139377842</v>
+        <v>-12.5647841698455</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000000927928134777204</v>
+        <v>0.00000150890504913905</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.67436160096497</v>
+        <v>-1.65283693658377</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.13333832464305</v>
+        <v>-1.14022809132355</v>
       </c>
     </row>
     <row r="25">
@@ -2930,22 +2930,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>-1.2207771640338</v>
+        <v>-1.17773223897253</v>
       </c>
       <c r="C25" t="n">
-        <v>0.109089167714756</v>
+        <v>0.108115699475087</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.1906359687872</v>
+        <v>-10.8932582843245</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00000139255678792348</v>
+        <v>0.00000446576434070282</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.46755400616343</v>
+        <v>-1.42704748904258</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.974000321904176</v>
+        <v>-0.928416988902493</v>
       </c>
     </row>
     <row r="26">
@@ -2953,22 +2953,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.50905610951238</v>
+        <v>-0.475808095365353</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0891984495554288</v>
+        <v>0.103271268120179</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.70700625458795</v>
+        <v>-4.60736179603841</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000291709483719402</v>
+        <v>0.00173864613071496</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.710837021084687</v>
+        <v>-0.713952066698264</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.307275197940072</v>
+        <v>-0.237664124032441</v>
       </c>
     </row>
     <row r="27">
@@ -2976,22 +2976,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.978668873912933</v>
+        <v>-0.927545745179019</v>
       </c>
       <c r="C27" t="n">
-        <v>0.15781171722437</v>
+        <v>0.153022257376905</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.20149689215727</v>
+        <v>-6.06150870519708</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000158580628697206</v>
+        <v>0.000302040483792354</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.33566378040553</v>
+        <v>-1.28041570346844</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.62167396742034</v>
+        <v>-0.5746757868896</v>
       </c>
     </row>
     <row r="28">
@@ -2999,22 +2999,22 @@
         <v>34</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.0178641891270201</v>
+        <v>0.387365944482442</v>
       </c>
       <c r="C28" t="n">
-        <v>0.085302030630612</v>
+        <v>0.239024432495377</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.209422788589622</v>
+        <v>1.62061233840576</v>
       </c>
       <c r="E28" t="n">
-        <v>0.838781824287036</v>
+        <v>0.143759544806778</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.210830788719291</v>
+        <v>-0.163825385266726</v>
       </c>
       <c r="G28" t="n">
-        <v>0.175102410465251</v>
+        <v>0.93855727423161</v>
       </c>
     </row>
     <row r="29">
@@ -3022,22 +3022,22 @@
         <v>35</v>
       </c>
       <c r="B29" t="n">
-        <v>1.67704028157526</v>
+        <v>1.61847997347001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.242190971600674</v>
+        <v>0.343392524292571</v>
       </c>
       <c r="D29" t="n">
-        <v>6.92445416314022</v>
+        <v>4.71320677933881</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0000687704948888304</v>
+        <v>0.00151538873014888</v>
       </c>
       <c r="F29" t="n">
-        <v>1.12916624040374</v>
+        <v>0.826615392453147</v>
       </c>
       <c r="G29" t="n">
-        <v>2.22491432274678</v>
+        <v>2.41034455448688</v>
       </c>
     </row>
     <row r="30">
@@ -3045,22 +3045,22 @@
         <v>36</v>
       </c>
       <c r="B30" t="n">
-        <v>0.000376457388476008</v>
+        <v>0.00230114558426336</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00384059234373959</v>
+        <v>0.00286477062597288</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0980206579564889</v>
+        <v>0.803256485318748</v>
       </c>
       <c r="E30" t="n">
-        <v>0.924064216718681</v>
+        <v>0.445034418016337</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.00831156609130245</v>
+        <v>-0.00430502732564152</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00906448086825447</v>
+        <v>0.00890731849416825</v>
       </c>
     </row>
   </sheetData>

--- a/Statistical_documentation_in_R/main_results/saturated_models.xlsx
+++ b/Statistical_documentation_in_R/main_results/saturated_models.xlsx
@@ -6,10 +6,11 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="m_sat_DK" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="m_sat_DK2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="m_sat_DK3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="s4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="weighted_country_year_FE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="weighted_country_FE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="weighted_no_FE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="weighted_country_year_controls" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="unweighted_country_year_FE" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -122,7 +123,7 @@
     <t xml:space="preserve">c_log_GDPpc</t>
   </si>
   <si>
-    <t xml:space="preserve">c_log_Pop15_65</t>
+    <t xml:space="preserve">c_log_Pop15_64</t>
   </si>
   <si>
     <t xml:space="preserve">c_YouthUnempl</t>
@@ -485,19 +486,19 @@
         <v>-0.548528315292826</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0534669507128421</v>
+        <v>0.0529198043509321</v>
       </c>
       <c r="D2" t="n">
-        <v>-10.2592032644397</v>
+        <v>-10.3652748157442</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0000028906092857989</v>
+        <v>0.00000265240622013023</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.66947896082086</v>
+        <v>-0.668241229759167</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.427577669764792</v>
+        <v>-0.428815400826486</v>
       </c>
     </row>
     <row r="3">
@@ -508,19 +509,19 @@
         <v>-0.602651188717814</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0668908829958757</v>
+        <v>0.0662063647521594</v>
       </c>
       <c r="D3" t="n">
-        <v>-9.00946678719987</v>
+        <v>-9.10261711202257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00000846492891050645</v>
+        <v>0.00000778105473323472</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.753968878812831</v>
+        <v>-0.752420390964742</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.451333498622797</v>
+        <v>-0.452881986470886</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +532,19 @@
         <v>-1.88714028053297</v>
       </c>
       <c r="C4" t="n">
-        <v>0.13227202699361</v>
+        <v>0.130918440215616</v>
       </c>
       <c r="D4" t="n">
-        <v>-14.2671154546089</v>
+        <v>-14.4146254524951</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000000174162194547103</v>
+        <v>0.00000015932451498817</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1863603938344</v>
+        <v>-2.1832983678091</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.58792016723154</v>
+        <v>-1.59098219325685</v>
       </c>
     </row>
     <row r="5">
@@ -554,19 +555,19 @@
         <v>-1.65473875502575</v>
       </c>
       <c r="C5" t="n">
-        <v>0.109942901142251</v>
+        <v>0.108817816262911</v>
       </c>
       <c r="D5" t="n">
-        <v>-15.0508922161763</v>
+        <v>-15.2065058080911</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000000109539617123382</v>
+        <v>0.000000100172887313859</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.90344687634351</v>
+        <v>-1.90090175752495</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.40603063370799</v>
+        <v>-1.40857575252654</v>
       </c>
     </row>
     <row r="6">
@@ -577,19 +578,19 @@
         <v>-0.902156900287866</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0680725118735046</v>
+        <v>0.0673759016028725</v>
       </c>
       <c r="D6" t="n">
-        <v>-13.2528810155308</v>
+        <v>-13.38990468143</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000000329051564751111</v>
+        <v>0.000000301179051302084</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.05614762061218</v>
+        <v>-1.05457177869879</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.748166179963551</v>
+        <v>-0.749742021876941</v>
       </c>
     </row>
     <row r="7">
@@ -600,19 +601,19 @@
         <v>-1.13719553654041</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0562244110472563</v>
+        <v>0.0556490466112132</v>
       </c>
       <c r="D7" t="n">
-        <v>-20.2260106483748</v>
+        <v>-20.4351306229075</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00000000822261862880283</v>
+        <v>0.00000000750904350872416</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.26438399071507</v>
+        <v>-1.26308242593486</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.01000708236575</v>
+        <v>-1.01130864714596</v>
       </c>
     </row>
     <row r="8">
@@ -623,19 +624,19 @@
         <v>-1.0464974377475</v>
       </c>
       <c r="C8" t="n">
-        <v>0.110556082289823</v>
+        <v>0.109424722509549</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.46576087061508</v>
+        <v>-9.56362889251269</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00000564030248496649</v>
+        <v>0.00000518092525234265</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.29659267119033</v>
+        <v>-1.29403335755969</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.796402204304674</v>
+        <v>-0.798961517935322</v>
       </c>
     </row>
     <row r="9">
@@ -646,19 +647,19 @@
         <v>-1.44743856438974</v>
       </c>
       <c r="C9" t="n">
-        <v>0.118991913499495</v>
+        <v>0.117774226852702</v>
       </c>
       <c r="D9" t="n">
-        <v>-12.1641758823879</v>
+        <v>-12.2899432504874</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00000068576909357595</v>
+        <v>0.000000628131238953298</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.71661697382769</v>
+        <v>-1.7138623752576</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.17826015495179</v>
+        <v>-1.18101475352188</v>
       </c>
     </row>
     <row r="10">
@@ -669,19 +670,19 @@
         <v>-1.75634080420609</v>
       </c>
       <c r="C10" t="n">
-        <v>0.208046479129221</v>
+        <v>0.205917465387079</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.44205973375399</v>
+        <v>-8.52934354501966</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0000143671620654869</v>
+        <v>0.0000132200779709318</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.22697463716321</v>
+        <v>-2.22215847347672</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.28570697124897</v>
+        <v>-1.29052313493546</v>
       </c>
     </row>
     <row r="11">
@@ -689,22 +690,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.597099568405569</v>
+        <v>-0.59709956840557</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0622419851518707</v>
+        <v>0.061605040735681</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.59319608699247</v>
+        <v>-9.69238168297705</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00000505036821286527</v>
+        <v>0.00000463818669297399</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.737900720943653</v>
+        <v>-0.736459852570266</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.456298415867486</v>
+        <v>-0.457739284240874</v>
       </c>
     </row>
     <row r="12">
@@ -712,22 +713,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.68149440447416</v>
+        <v>-0.681494404474159</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0728890562416123</v>
+        <v>0.0721431565551221</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.34974932608738</v>
+        <v>-9.44641788654552</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00000624384535664096</v>
+        <v>0.00000573630424502743</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.846380905140724</v>
+        <v>-0.844693562822201</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.516607903807595</v>
+        <v>-0.518295246126118</v>
       </c>
     </row>
     <row r="13">
@@ -738,19 +739,19 @@
         <v>-0.865743632479564</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0788473562973175</v>
+        <v>0.0780404832047174</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.9799956921196</v>
+        <v>-11.0935196314524</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00000163483267816503</v>
+        <v>0.00000149894592475823</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.04410874429524</v>
+        <v>-1.04228347054935</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.687378520663885</v>
+        <v>-0.68920379440978</v>
       </c>
     </row>
     <row r="14">
@@ -761,19 +762,19 @@
         <v>-1.11446172081908</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0778409861728348</v>
+        <v>0.0770444116237276</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.3171582942767</v>
+        <v>-14.4651856939596</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000000168963696892027</v>
+        <v>0.000000154565249181855</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.29055026524924</v>
+        <v>-1.28874828842727</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.938373176388928</v>
+        <v>-0.940175153210894</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +785,19 @@
         <v>-0.925030716865115</v>
       </c>
       <c r="C15" t="n">
-        <v>0.113259883054427</v>
+        <v>0.112100854317096</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.16732890692277</v>
+        <v>-8.25177223224821</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0000187537200247716</v>
+        <v>0.0000172661857066783</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.18124237257437</v>
+        <v>-1.17862046741433</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.668819061155855</v>
+        <v>-0.671440966315898</v>
       </c>
     </row>
     <row r="16">
@@ -807,19 +808,19 @@
         <v>-1.51151031782695</v>
       </c>
       <c r="C16" t="n">
-        <v>0.128185980265557</v>
+        <v>0.126874207458583</v>
       </c>
       <c r="D16" t="n">
-        <v>-11.7915415921119</v>
+        <v>-11.9134562343601</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000000893826164933692</v>
+        <v>0.000000818937939670571</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.80148715125499</v>
+        <v>-1.79851971500373</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.22153348439891</v>
+        <v>-1.22450092065017</v>
       </c>
     </row>
     <row r="17">
@@ -830,19 +831,19 @@
         <v>-2.1731071022163</v>
       </c>
       <c r="C17" t="n">
-        <v>0.280103720890888</v>
+        <v>0.277237319723159</v>
       </c>
       <c r="D17" t="n">
-        <v>-7.75822290151876</v>
+        <v>-7.83843641392257</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000028260996074205</v>
+        <v>0.0000260437820937054</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.80674574075605</v>
+        <v>-2.80026149082302</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.53946846367655</v>
+        <v>-1.54595271360958</v>
       </c>
     </row>
     <row r="18">
@@ -850,22 +851,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.492889178451345</v>
+        <v>-0.492889178451346</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0474357484335302</v>
+        <v>0.0469503215107349</v>
       </c>
       <c r="D18" t="n">
-        <v>-10.3906693733738</v>
+        <v>-10.498100174642</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0000025986452743028</v>
+        <v>0.00000238413718945317</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.600196296542949</v>
+        <v>-0.599098184552533</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.385582060359741</v>
+        <v>-0.386680172350158</v>
       </c>
     </row>
     <row r="19">
@@ -876,19 +877,19 @@
         <v>-0.361672972880734</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0453451950895721</v>
+        <v>0.0448811615466068</v>
       </c>
       <c r="D19" t="n">
-        <v>-7.97599331453549</v>
+        <v>-8.05845839139336</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0000226725427225232</v>
+        <v>0.0000208830197827874</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.464250930751092</v>
+        <v>-0.463201213948094</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.259095015010377</v>
+        <v>-0.260144731813375</v>
       </c>
     </row>
     <row r="20">
@@ -899,19 +900,19 @@
         <v>-0.534966490387353</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0242067647960702</v>
+        <v>0.0239590483320634</v>
       </c>
       <c r="D20" t="n">
-        <v>-22.0998755882571</v>
+        <v>-22.3283697654815</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0000000037576566361607</v>
+        <v>0.00000000343057777963834</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.589725996758954</v>
+        <v>-0.589165623185558</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.480206984015751</v>
+        <v>-0.480767357589147</v>
       </c>
     </row>
     <row r="21">
@@ -922,19 +923,19 @@
         <v>-1.66827531130462</v>
       </c>
       <c r="C21" t="n">
-        <v>0.150710761330213</v>
+        <v>0.149168484414276</v>
       </c>
       <c r="D21" t="n">
-        <v>-11.0693841407209</v>
+        <v>-11.1838322810295</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00000152675740010926</v>
+        <v>0.00000139973203504981</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.00920673955854</v>
+        <v>-2.00571786678613</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.32734388305071</v>
+        <v>-1.33083275582312</v>
       </c>
     </row>
     <row r="22">
@@ -945,19 +946,19 @@
         <v>-0.939163094176183</v>
       </c>
       <c r="C22" t="n">
-        <v>0.353432189076277</v>
+        <v>0.349815391569496</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.65726530633998</v>
+        <v>-2.68473919904581</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0261627912024229</v>
+        <v>0.0250111275138446</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.73868225225853</v>
+        <v>-1.73050048787218</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.139643936093834</v>
+        <v>-0.14782570048019</v>
       </c>
     </row>
     <row r="23">
@@ -968,19 +969,19 @@
         <v>-1.71142660425998</v>
       </c>
       <c r="C23" t="n">
-        <v>0.13749860491786</v>
+        <v>0.136091532705334</v>
       </c>
       <c r="D23" t="n">
-        <v>-12.4468652266135</v>
+        <v>-12.5755553651201</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000000563594216171157</v>
+        <v>0.00000051612005074096</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.02247005824967</v>
+        <v>-2.01928703976553</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.40038315027028</v>
+        <v>-1.40356616875442</v>
       </c>
     </row>
     <row r="24">
@@ -991,19 +992,19 @@
         <v>-1.51631980729154</v>
       </c>
       <c r="C24" t="n">
-        <v>0.120034527600492</v>
+        <v>0.118806171513386</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.6323636840415</v>
+        <v>-12.7629717208815</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000000496584401113989</v>
+        <v>0.000000454697238621993</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.78785677368609</v>
+        <v>-1.78507803916517</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.24478284089698</v>
+        <v>-1.2475615754179</v>
       </c>
     </row>
     <row r="25">
@@ -1014,19 +1015,19 @@
         <v>-1.27954849138055</v>
       </c>
       <c r="C25" t="n">
-        <v>0.122301721247697</v>
+        <v>0.121050164161065</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.4622279909625</v>
+        <v>-10.5703986462839</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00000245351015945265</v>
+        <v>0.00000225079998123731</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.55621420612358</v>
+        <v>-1.55338298729541</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.00288277663753</v>
+        <v>-1.0057139954657</v>
       </c>
     </row>
     <row r="26">
@@ -1034,22 +1035,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.507694623110318</v>
+        <v>-0.507694623110317</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0840744526071487</v>
+        <v>0.0832140887761177</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.03863132457848</v>
+        <v>-6.10106570386462</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000193148115048323</v>
+        <v>0.000179012910458533</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.697884248283917</v>
+        <v>-0.695937970080938</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.317504997936718</v>
+        <v>-0.319451276139697</v>
       </c>
     </row>
     <row r="27">
@@ -1060,19 +1061,19 @@
         <v>-0.966842771143045</v>
       </c>
       <c r="C27" t="n">
-        <v>0.141019369576385</v>
+        <v>0.139576268124338</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.8560990880004</v>
+        <v>-6.92698539755884</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0000742243536878554</v>
+        <v>0.0000685771277266244</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.28585074812355</v>
+        <v>-1.28258622583716</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.647834794162538</v>
+        <v>-0.651099316448931</v>
       </c>
     </row>
   </sheetData>
@@ -1111,623 +1112,600 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>6.84425645524675</v>
+        <v>-0.52521278065546</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0318759503030344</v>
+        <v>0.0513360287051052</v>
       </c>
       <c r="D2" t="n">
-        <v>214.715369743666</v>
+        <v>-10.2308806096493</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00000000000000000524512488362617</v>
+        <v>0.00000295813684482266</v>
       </c>
       <c r="F2" t="n">
-        <v>6.77214804594774</v>
+        <v>-0.641342945700328</v>
       </c>
       <c r="G2" t="n">
-        <v>6.91636486454576</v>
+        <v>-0.409082615610592</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.960965940404461</v>
+        <v>-0.579335654080448</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0461162074049813</v>
+        <v>0.0634420688936834</v>
       </c>
       <c r="D3" t="n">
-        <v>-20.8379221640126</v>
+        <v>-9.13172700990099</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00000000632015515319226</v>
+        <v>0.00000757999082911671</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.06528804930673</v>
+        <v>-0.722851584651031</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.856643831502194</v>
+        <v>-0.435819723509865</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.434022554195918</v>
+        <v>-1.86382474589559</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0590620907269248</v>
+        <v>0.128181235983655</v>
       </c>
       <c r="D4" t="n">
-        <v>-7.34858094005905</v>
+        <v>-14.5405427837601</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0000433384158119921</v>
+        <v>0.000000147761221233618</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.567630285783668</v>
+        <v>-2.15379084701234</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.300414822608167</v>
+        <v>-1.57385864477883</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.00653677484273</v>
+        <v>-1.63142322038839</v>
       </c>
       <c r="C5" t="n">
-        <v>0.100972759744255</v>
+        <v>0.104907220100604</v>
       </c>
       <c r="D5" t="n">
-        <v>-9.96839917411489</v>
+        <v>-15.5511052416019</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00000367373570514733</v>
+        <v>0.0000000824298978110872</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2349530265457</v>
+        <v>-1.86873983976822</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.778120523139761</v>
+        <v>-1.39410660100856</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>-2.57228792204316</v>
+        <v>-0.878841365650511</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0979942669188626</v>
+        <v>0.0658715237517957</v>
       </c>
       <c r="D6" t="n">
-        <v>-26.2493715491843</v>
+        <v>-13.3417494479404</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000000000816098049987775</v>
+        <v>0.000000310665230121364</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.79396635486683</v>
+        <v>-1.02785310493007</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.3506094892195</v>
+        <v>-0.729829626370955</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>0.254871091504826</v>
+        <v>-1.11388000190306</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0419510586743386</v>
+        <v>0.051461734760974</v>
       </c>
       <c r="D7" t="n">
-        <v>6.07543884609355</v>
+        <v>-21.6448203131265</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000184673870099437</v>
+        <v>0.00000000451724824360409</v>
       </c>
       <c r="F7" t="n">
-        <v>0.159971203637704</v>
+        <v>-1.23029453380261</v>
       </c>
       <c r="G7" t="n">
-        <v>0.349770979371949</v>
+        <v>-0.997465470003498</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.901080379826354</v>
+        <v>-1.02318190311013</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0519907578194989</v>
+        <v>0.104811888332898</v>
       </c>
       <c r="D8" t="n">
-        <v>-17.331549252556</v>
+        <v>-9.76207870485415</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000000319796336726987</v>
+        <v>0.00000437075375282675</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.01869164502704</v>
+        <v>-1.2602828670488</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.783469114625668</v>
+        <v>-0.786080939171462</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.60940984121378</v>
+        <v>-1.42412302975238</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0932058688703385</v>
+        <v>0.114932572492539</v>
       </c>
       <c r="D9" t="n">
-        <v>-17.2672586042053</v>
+        <v>-12.3909436538961</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0000000330379976908486</v>
+        <v>0.000000585711890781053</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.82025616509365</v>
+        <v>-1.6841185718552</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.39856351733392</v>
+        <v>-1.16412748764956</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>-2.23730001977715</v>
+        <v>-1.73302526956871</v>
       </c>
       <c r="C10" t="n">
-        <v>0.104042028035925</v>
+        <v>0.203662373465885</v>
       </c>
       <c r="D10" t="n">
-        <v>-21.5038101622225</v>
+        <v>-8.50930508211427</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00000000478608473763055</v>
+        <v>0.0000134742322881345</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.47265943873067</v>
+        <v>-2.19374156649704</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.00194060082364</v>
+        <v>-1.27230897264037</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.81724372925606</v>
+        <v>-0.573784033768207</v>
       </c>
       <c r="C11" t="n">
-        <v>0.174308582205283</v>
+        <v>0.0585073042169365</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.4254403671065</v>
+        <v>-9.80704958889748</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00000252697349455325</v>
+        <v>0.00000420723614452584</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.21155713702894</v>
+        <v>-0.706136751078563</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.42293032148318</v>
+        <v>-0.44143131645785</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>1.17878238242509</v>
+        <v>-0.658178869836797</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0602982977496543</v>
+        <v>0.0705290026591714</v>
       </c>
       <c r="D12" t="n">
-        <v>19.5491817583167</v>
+        <v>-9.33203143418063</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0000000111007440125213</v>
+        <v>0.00000634212807224272</v>
       </c>
       <c r="F12" t="n">
-        <v>1.04237815626617</v>
+        <v>-0.817726558387255</v>
       </c>
       <c r="G12" t="n">
-        <v>1.31518660858401</v>
+        <v>-0.498631181286338</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>0.652016052811823</v>
+        <v>-0.842428097842199</v>
       </c>
       <c r="C13" t="n">
-        <v>0.063170118710207</v>
+        <v>0.0778939400069811</v>
       </c>
       <c r="D13" t="n">
-        <v>10.3215897979066</v>
+        <v>-10.8150659443687</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00000274778173583764</v>
+        <v>0.0000018571094093898</v>
       </c>
       <c r="F13" t="n">
-        <v>0.509115316296715</v>
+        <v>-1.01863643216757</v>
       </c>
       <c r="G13" t="n">
-        <v>0.794916789326931</v>
+        <v>-0.666219763516833</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>0.105148204123416</v>
+        <v>-1.09114618618171</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0769206826843501</v>
+        <v>0.0745419858467081</v>
       </c>
       <c r="D14" t="n">
-        <v>1.36696920066219</v>
+        <v>-14.6380080137066</v>
       </c>
       <c r="E14" t="n">
-        <v>0.204803829305569</v>
+        <v>0.000000139447850732648</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0688584691783142</v>
+        <v>-1.25977187339405</v>
       </c>
       <c r="G14" t="n">
-        <v>0.279154877425147</v>
+        <v>-0.922520498969381</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.03193334005775</v>
+        <v>-0.901715182227752</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0733849890529598</v>
+        <v>0.110411976526741</v>
       </c>
       <c r="D15" t="n">
-        <v>-14.0619131156787</v>
+        <v>-8.1668240221147</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00000019740955534668</v>
+        <v>0.0000187630266796512</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.19794171868577</v>
+        <v>-1.15148442578643</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.865924961429732</v>
+        <v>-0.651945938669078</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>0.676484214286659</v>
+        <v>-1.48819478318959</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0975322589393085</v>
+        <v>0.121586031291358</v>
       </c>
       <c r="D16" t="n">
-        <v>6.93600478081428</v>
+        <v>-12.2398499842751</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0000678929312231913</v>
+        <v>0.000000650420893441123</v>
       </c>
       <c r="F16" t="n">
-        <v>0.455850916123213</v>
+        <v>-1.76324149477154</v>
       </c>
       <c r="G16" t="n">
-        <v>0.897117512450105</v>
+        <v>-1.21314807160764</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.9283884570794</v>
+        <v>-2.14979156757895</v>
       </c>
       <c r="C17" t="n">
-        <v>0.121957389983962</v>
+        <v>0.270911413958599</v>
       </c>
       <c r="D17" t="n">
-        <v>-15.8119852952986</v>
+        <v>-7.93540418310865</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0000000713094202898203</v>
+        <v>0.0000236145988519193</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2042752403878</v>
+        <v>-2.76263576314918</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.65250167377101</v>
+        <v>-1.53694737200871</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.41154374670083</v>
+        <v>-0.469573643813987</v>
       </c>
       <c r="C18" t="n">
-        <v>0.243767161580106</v>
+        <v>0.0400360300919069</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.79054101278927</v>
+        <v>-11.7287763730828</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000262569691071064</v>
+        <v>0.000000935307105741613</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.96298337732426</v>
+        <v>-0.560141436056399</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.860104116077409</v>
+        <v>-0.379005851571576</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.23682720068211</v>
+        <v>-0.338357438243378</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0402818268883593</v>
+        <v>0.0488065406715088</v>
       </c>
       <c r="D19" t="n">
-        <v>-30.7043472509318</v>
+        <v>-6.93262488158471</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000000000201925194807998</v>
+        <v>0.0000681484471430512</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.32795102390821</v>
+        <v>-0.448765503814834</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.14570337745601</v>
+        <v>-0.227949372671922</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>-2.33542460306685</v>
+        <v>-0.511650955749995</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0413003455977453</v>
+        <v>0.0260234081289855</v>
       </c>
       <c r="D20" t="n">
-        <v>-56.5473380250442</v>
+        <v>-19.6611817027957</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00000000000085146669966162</v>
+        <v>0.0000000105557086638335</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.42885247568683</v>
+        <v>-0.5705199948494</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.24199673044687</v>
+        <v>-0.452781916650589</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.491491140953966</v>
+        <v>-1.64495977666726</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0365741441006284</v>
+        <v>0.145599324590239</v>
       </c>
       <c r="D21" t="n">
-        <v>-13.4382130611642</v>
+        <v>-11.2978530724416</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000000291983572926226</v>
+        <v>0.00000128468420917581</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.574227603004417</v>
+        <v>-1.97432833168765</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.408754678903516</v>
+        <v>-1.31559122164687</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.135467924196604</v>
+        <v>-0.915847559538823</v>
       </c>
       <c r="C22" t="n">
-        <v>0.141079854254474</v>
+        <v>0.344612616834039</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.960221605788258</v>
+        <v>-2.65761470938797</v>
       </c>
       <c r="E22" t="n">
-        <v>0.362028727944162</v>
+        <v>0.0261478135539984</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.454612727024889</v>
+        <v>-1.69541545910058</v>
       </c>
       <c r="G22" t="n">
-        <v>0.18367687863168</v>
+        <v>-0.136279659977068</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.0871012334289815</v>
+        <v>-1.68811106962261</v>
       </c>
       <c r="C23" t="n">
-        <v>0.320623413352701</v>
+        <v>0.132956756494873</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.27166211137914</v>
+        <v>-12.6966926249266</v>
       </c>
       <c r="E23" t="n">
-        <v>0.792010618188725</v>
+        <v>0.00000047544351402172</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.812401784505604</v>
+        <v>-1.98888014866991</v>
       </c>
       <c r="G23" t="n">
-        <v>0.638199317647641</v>
+        <v>-1.38734199057532</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.363229088282855</v>
+        <v>-1.49300427265418</v>
       </c>
       <c r="C24" t="n">
-        <v>0.129515330275425</v>
+        <v>0.118625375226096</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.80452582339417</v>
+        <v>-12.5858760809698</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0205600655629247</v>
+        <v>0.000000512508640327437</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.656213120357582</v>
+        <v>-1.76135351491152</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0702450562081269</v>
+        <v>-1.22465503039685</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>-1.570149434979</v>
+        <v>-1.2562329567432</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0941387088949282</v>
+        <v>0.119899353377038</v>
       </c>
       <c r="D25" t="n">
-        <v>-16.6791052629743</v>
+        <v>-10.4773955935594</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0000000447440901221243</v>
+        <v>0.00000242390960166908</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.78310598960224</v>
+        <v>-1.52746413779994</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.35719288035576</v>
+        <v>-0.98500177568646</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>-3.10774363053025</v>
+        <v>-0.484379088472961</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0938094532379969</v>
+        <v>0.0788357768229843</v>
       </c>
       <c r="D26" t="n">
-        <v>-33.1282565163858</v>
+        <v>-6.14415317503083</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000000000102464289254154</v>
+        <v>0.000169915872999393</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.31995535711077</v>
+        <v>-0.662718005697836</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.89553190394974</v>
+        <v>-0.306040171248086</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>0.964333655223479</v>
+        <v>-0.943527236505687</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0647709482273757</v>
+        <v>0.137914006032362</v>
       </c>
       <c r="D27" t="n">
-        <v>14.8883671092513</v>
+        <v>-6.84141708046884</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000000120369740444907</v>
+        <v>0.0000754564167113887</v>
       </c>
       <c r="F27" t="n">
-        <v>0.81781159074969</v>
+        <v>-1.25551039310199</v>
       </c>
       <c r="G27" t="n">
-        <v>1.11085571969727</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" t="n">
-        <v>-0.629643708398587</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.123749266909758</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-5.08806010832973</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.000655646609455301</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-0.909583998929522</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-0.349703417867651</v>
+        <v>-0.631544079909384</v>
       </c>
     </row>
   </sheetData>
@@ -1766,600 +1744,623 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.686029434169956</v>
+        <v>6.84425645524675</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0806350371862693</v>
+        <v>0.0318759502896212</v>
       </c>
       <c r="D2" t="n">
-        <v>-8.50783304762678</v>
+        <v>214.715369834017</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0000134931131924825</v>
+        <v>0.00000000000000000524512486376562</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.868438561113375</v>
+        <v>6.77214804597809</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.503620307226538</v>
+        <v>6.91636486451542</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.740152307594946</v>
+        <v>-0.96096594040446</v>
       </c>
       <c r="C3" t="n">
-        <v>0.094411981683629</v>
+        <v>0.0461162073950911</v>
       </c>
       <c r="D3" t="n">
-        <v>-7.83960144036768</v>
+        <v>-20.8379221684815</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000260130184722503</v>
+        <v>0.00000000632015514121853</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.95372704821454</v>
+        <v>-1.06528804928435</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.526577566975351</v>
+        <v>-0.856643831524567</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>-2.02464139941014</v>
+        <v>-0.434022554195918</v>
       </c>
       <c r="C4" t="n">
-        <v>0.159778821269735</v>
+        <v>0.059062090718878</v>
       </c>
       <c r="D4" t="n">
-        <v>-12.6715254457422</v>
+        <v>-7.34858094106024</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000000483593539550033</v>
+        <v>0.0000433384157657676</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.38608620440892</v>
+        <v>-0.567630285765465</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.66319659441135</v>
+        <v>-0.300414822626371</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.7922398739029</v>
+        <v>-1.00653677484273</v>
       </c>
       <c r="C5" t="n">
-        <v>0.13122033924718</v>
+        <v>0.100972759739992</v>
       </c>
       <c r="D5" t="n">
-        <v>-13.6582475261465</v>
+        <v>-9.96839917453571</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000000253849769978788</v>
+        <v>0.00000367373570385704</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.08908090423572</v>
+        <v>-1.23495302653605</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.49539884357009</v>
+        <v>-0.778120523149404</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.039658019165</v>
+        <v>-2.57228792204316</v>
       </c>
       <c r="C6" t="n">
-        <v>0.097164807092031</v>
+        <v>0.0979942669145068</v>
       </c>
       <c r="D6" t="n">
-        <v>-10.6999442522463</v>
+        <v>-26.2493715503511</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00000203197995620292</v>
+        <v>0.000000000816098049665129</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.25946008350015</v>
+        <v>-2.79396635485697</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.819855954829858</v>
+        <v>-2.35060948922935</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.27469665541755</v>
+        <v>0.254871091504826</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0653617641267056</v>
+        <v>0.0419510586632492</v>
       </c>
       <c r="D7" t="n">
-        <v>-19.5021764245304</v>
+        <v>6.07543884769954</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00000001133872648898</v>
+        <v>0.000184673869738631</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.42255523830991</v>
+        <v>0.15997120366279</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1268380725252</v>
+        <v>0.349770979346863</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.18399855662465</v>
+        <v>-0.901080379826354</v>
       </c>
       <c r="C8" t="n">
-        <v>0.133662157307294</v>
+        <v>0.0519907578106493</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.85814340032381</v>
+        <v>-17.331549255506</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00000972123719727481</v>
+        <v>0.0000000319796336250043</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4863633631724</v>
+        <v>-1.01869164500702</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.881633750076891</v>
+        <v>-0.783469114645687</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.58493968326689</v>
+        <v>-1.60940984121379</v>
       </c>
       <c r="C9" t="n">
-        <v>0.145137238850082</v>
+        <v>0.0932058688661739</v>
       </c>
       <c r="D9" t="n">
-        <v>-10.9202827325662</v>
+        <v>-17.2672586049769</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00000171172354240193</v>
+        <v>0.0000000330379976779168</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.91326292772036</v>
+        <v>-1.82025616508423</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.25661643881342</v>
+        <v>-1.39856351734334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.89384192308325</v>
+        <v>-2.23730001977715</v>
       </c>
       <c r="C10" t="n">
-        <v>0.234770840910489</v>
+        <v>0.104042028031447</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.06676806940142</v>
+        <v>-21.5038101631479</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0000207114770395012</v>
+        <v>0.00000000478608473580891</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.42493046246507</v>
+        <v>-2.47265943872054</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.36275338370143</v>
+        <v>-2.00194060083376</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.734600687282701</v>
+        <v>-1.81724372925606</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0860363017740823</v>
+        <v>0.174308582203554</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.53826433883276</v>
+        <v>-10.4254403672099</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0000131086313287898</v>
+        <v>0.0000025269734943434</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.929228323601609</v>
+        <v>-2.21155713702503</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.539973050963793</v>
+        <v>-1.42293032148709</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.818995523351293</v>
+        <v>1.17878238242509</v>
       </c>
       <c r="C12" t="n">
-        <v>0.101102927879743</v>
+        <v>0.0602982977417575</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.10061133269505</v>
+        <v>19.5491817608769</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0000200286306649246</v>
+        <v>0.0000000111007439997111</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.04770623583432</v>
+        <v>1.04237815628404</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.590284810868263</v>
+        <v>1.31518660856615</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.0032447513567</v>
+        <v>0.652016052811823</v>
       </c>
       <c r="C13" t="n">
-        <v>0.104029127924561</v>
+        <v>0.0631701187027887</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.64388312554372</v>
+        <v>10.3215897991187</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00000483490319455167</v>
+        <v>0.00000274778173313939</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2385749882309</v>
+        <v>0.509115316313497</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.767914514482506</v>
+        <v>0.794916789310149</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.25196283969623</v>
+        <v>0.105148204123416</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0902364497281951</v>
+        <v>0.0769206826785055</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.8742475293223</v>
+        <v>1.36696920076605</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000000221705430784416</v>
+        <v>0.204803829274186</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.45609187079434</v>
+        <v>-0.068858469165093</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.04783380859811</v>
+        <v>0.279154877411925</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.06253183574225</v>
+        <v>-1.03193334005775</v>
       </c>
       <c r="C15" t="n">
-        <v>0.140052834386644</v>
+        <v>0.0733849890470694</v>
       </c>
       <c r="D15" t="n">
-        <v>-7.5866499981637</v>
+        <v>-14.0619131168074</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0000337315354370468</v>
+        <v>0.000000197409555209717</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.37935335822019</v>
+        <v>-1.19794171867245</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.745710313264316</v>
+        <v>-0.865924961443057</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.6490114367041</v>
+        <v>0.67648421428666</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1469610057312</v>
+        <v>0.097532258934755</v>
       </c>
       <c r="D16" t="n">
-        <v>-11.2207413694503</v>
+        <v>6.9360047811381</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00000136129096033777</v>
+        <v>0.0000678929311987609</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.98146032847097</v>
+        <v>0.455850916133514</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.31656254493724</v>
+        <v>0.897117512439805</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" t="n">
-        <v>-2.31060822109347</v>
+        <v>-1.9283884570794</v>
       </c>
       <c r="C17" t="n">
-        <v>0.300379977021704</v>
+        <v>0.121957389980216</v>
       </c>
       <c r="D17" t="n">
-        <v>-7.69228443254898</v>
+        <v>-15.8119852957843</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0000302389818950116</v>
+        <v>0.0000000713094202707285</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.99011493767428</v>
+        <v>-2.20427524037932</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.63110150451267</v>
+        <v>-1.65250167377949</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.630390297328473</v>
+        <v>-1.41154374670083</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0684229491726902</v>
+        <v>0.243767161579299</v>
       </c>
       <c r="D18" t="n">
-        <v>-9.2131412771679</v>
+        <v>-5.79054101280843</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00000704738018333912</v>
+        <v>0.000262569691064757</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.785173761899252</v>
+        <v>-1.96298337732243</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.475606832757695</v>
+        <v>-0.860104116079233</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.499174091757858</v>
+        <v>-1.23682720068211</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0491984519509833</v>
+        <v>0.0402818268782827</v>
       </c>
       <c r="D19" t="n">
-        <v>-10.1461341152601</v>
+        <v>-30.7043472586126</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00000317080178437395</v>
+        <v>0.000000000201925194357295</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.610468722237359</v>
+        <v>-1.32795102388541</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.387879461278358</v>
+        <v>-1.1457033774788</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.672467609264481</v>
+        <v>-2.33542460306685</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0474101741768533</v>
+        <v>0.0413003455872861</v>
       </c>
       <c r="D20" t="n">
-        <v>-14.1840358307056</v>
+        <v>-56.5473380393647</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000000183187957058367</v>
+        <v>0.000000000000851466697725885</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.77971687436816</v>
+        <v>-2.42885247566317</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.565218344160802</v>
+        <v>-2.24199673047053</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.80577643018178</v>
+        <v>-0.491491140953967</v>
       </c>
       <c r="C21" t="n">
-        <v>0.165775806747522</v>
+        <v>0.0365741440885233</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.8928827771111</v>
+        <v>-13.4382130656119</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00000174833460437582</v>
+        <v>0.000000291983572094035</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.18078735883434</v>
+        <v>-0.574227602977033</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.43076550152922</v>
+        <v>-0.4087546789309</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.07666421305332</v>
+        <v>-0.135467924196604</v>
       </c>
       <c r="C22" t="n">
-        <v>0.365928882571068</v>
+        <v>0.141079854251251</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.94227721378134</v>
+        <v>-0.960221605810197</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0164258161362276</v>
+        <v>0.362028727933707</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.90445285583621</v>
+        <v>-0.454612727017598</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.248875570270436</v>
+        <v>0.183676878624389</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.84892772313713</v>
+        <v>-0.0871012334289818</v>
       </c>
       <c r="C23" t="n">
-        <v>0.158605950994889</v>
+        <v>0.320623413352174</v>
       </c>
       <c r="D23" t="n">
-        <v>-11.6573666469597</v>
+        <v>-0.271662111379588</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000000985106242712093</v>
+        <v>0.792010618188392</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.20771931124264</v>
+        <v>-0.812401784504412</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.49013613503163</v>
+        <v>0.638199317646448</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.65382092616869</v>
+        <v>-0.363229088282854</v>
       </c>
       <c r="C24" t="n">
-        <v>0.126215053332224</v>
+        <v>0.129515330272054</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.1031987271399</v>
+        <v>-2.80452582346716</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000000362802730012301</v>
+        <v>0.0205600655604734</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.93933921311714</v>
+        <v>-0.656213120349957</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.36830263922024</v>
+        <v>-0.070245056215752</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" t="n">
-        <v>-1.4170496102577</v>
+        <v>-1.570149434979</v>
       </c>
       <c r="C25" t="n">
-        <v>0.148965986928393</v>
+        <v>0.0941387088909769</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.51257155728352</v>
+        <v>-16.6791052636743</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00000541521511403471</v>
+        <v>0.0000000447440901057035</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.75403408460107</v>
+        <v>-1.7831059895933</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.08006513591433</v>
+        <v>-1.3571928803647</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.645195741987445</v>
+        <v>-3.10774363053025</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0866337880240139</v>
+        <v>0.0938094532359763</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.44739156284617</v>
+        <v>-33.1282565170993</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0000390287012760679</v>
+        <v>0.000000000102464289234438</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.841174986106309</v>
+        <v>-3.3199553571062</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.44921649786858</v>
+        <v>-2.89553190395431</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.964333655223479</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0647709482201742</v>
+      </c>
+      <c r="D27" t="n">
+        <v>14.8883671109066</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.000000120369740328734</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.81781159076598</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.11085571968098</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
         <v>32</v>
       </c>
-      <c r="B27" t="n">
-        <v>-1.10434389002018</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.167432131026498</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-6.59577037722473</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.0000997598952006276</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-1.48310168450434</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-0.725586095536024</v>
+      <c r="B28" t="n">
+        <v>-0.629643708398586</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.123749266906446</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-5.08806010846588</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.000655646609334598</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.90958399892203</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.349703417875142</v>
       </c>
     </row>
   </sheetData>
@@ -2401,22 +2402,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.503946176716643</v>
+        <v>-0.50418333895697</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0576967756870042</v>
+        <v>0.057191415099473</v>
       </c>
       <c r="D2" t="n">
-        <v>-8.73439062609792</v>
+        <v>-8.81571715055563</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0000230842042934912</v>
+        <v>0.0000215698323908249</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.636995180038822</v>
+        <v>-0.636066978674533</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.370897173394465</v>
+        <v>-0.372299699239408</v>
       </c>
     </row>
     <row r="3">
@@ -2424,22 +2425,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.575214185091174</v>
+        <v>-0.575106484720285</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0688147154075705</v>
+        <v>0.068108398957778</v>
       </c>
       <c r="D3" t="n">
-        <v>-8.35888344061789</v>
+        <v>-8.4439877242865</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000317975072158554</v>
+        <v>0.0000295412627749689</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.733901203383929</v>
+        <v>-0.732164734359056</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.416527166798418</v>
+        <v>-0.418048235081514</v>
       </c>
     </row>
     <row r="4">
@@ -2447,22 +2448,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.78201274145107</v>
+        <v>-1.78074316952686</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1066149052213</v>
+        <v>0.104921952132519</v>
       </c>
       <c r="D4" t="n">
-        <v>-16.7144803791941</v>
+        <v>-16.9720743212796</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000000166082238424151</v>
+        <v>0.000000147400561615346</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.02786715376579</v>
+        <v>-2.02269362501814</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.53615832913635</v>
+        <v>-1.53879271403557</v>
       </c>
     </row>
     <row r="5">
@@ -2470,22 +2471,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.53077579845466</v>
+        <v>-1.52949555936864</v>
       </c>
       <c r="C5" t="n">
-        <v>0.102203062300632</v>
+        <v>0.100664168994638</v>
       </c>
       <c r="D5" t="n">
-        <v>-14.9777879840025</v>
+        <v>-15.1940414811362</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000000389795619605741</v>
+        <v>0.00000034878281599872</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.76645648275045</v>
+        <v>-1.76162754933717</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.29509511415888</v>
+        <v>-1.29736356940011</v>
       </c>
     </row>
     <row r="6">
@@ -2493,22 +2494,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.944731756786608</v>
+        <v>-0.94367805969331</v>
       </c>
       <c r="C6" t="n">
-        <v>0.054810292421479</v>
+        <v>0.0538377666218375</v>
       </c>
       <c r="D6" t="n">
-        <v>-17.2363932949277</v>
+        <v>-17.5281799173025</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00000013064545416219</v>
+        <v>0.000000114584430139324</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.07112451776229</v>
+        <v>-1.06782817215342</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.818338995810928</v>
+        <v>-0.819527947233196</v>
       </c>
     </row>
     <row r="7">
@@ -2516,22 +2517,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.0754358809321</v>
+        <v>-1.07542954811253</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0725662391405374</v>
+        <v>0.0719487515470688</v>
       </c>
       <c r="D7" t="n">
-        <v>-14.8200581106225</v>
+        <v>-14.9471606523844</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000000423123206021077</v>
+        <v>0.000000396029743982673</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.24277392846639</v>
+        <v>-1.24134366670285</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.908097833397803</v>
+        <v>-0.909515429522212</v>
       </c>
     </row>
     <row r="8">
@@ -2539,22 +2540,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.02976256997693</v>
+        <v>-1.02963651354138</v>
       </c>
       <c r="C8" t="n">
-        <v>0.128539338040889</v>
+        <v>0.127175459408589</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.01126398868921</v>
+        <v>-8.09618866980747</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000432281503267705</v>
+        <v>0.0000400643056822194</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.32617481503562</v>
+        <v>-1.32290364883408</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.733350324918229</v>
+        <v>-0.736369378248683</v>
       </c>
     </row>
     <row r="9">
@@ -2562,22 +2563,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.4068736130427</v>
+        <v>-1.40656121795035</v>
       </c>
       <c r="C9" t="n">
-        <v>0.133034929578183</v>
+        <v>0.131723242436271</v>
       </c>
       <c r="D9" t="n">
-        <v>-10.5752197374291</v>
+        <v>-10.6781551375101</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00000558237511693736</v>
+        <v>0.0000051900386899434</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.71365271077658</v>
+        <v>-1.71031555971089</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.10009451530881</v>
+        <v>-1.10280687618981</v>
       </c>
     </row>
     <row r="10">
@@ -2585,22 +2586,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.62158572100424</v>
+        <v>-1.62221741722095</v>
       </c>
       <c r="C10" t="n">
-        <v>0.208046073389787</v>
+        <v>0.206271404031136</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.79435869460558</v>
+        <v>-7.86448041521101</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0000526457971858483</v>
+        <v>0.0000493726371537019</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.10134082655407</v>
+        <v>-2.09788012789112</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1418306154544</v>
+        <v>-1.14655470655078</v>
       </c>
     </row>
     <row r="11">
@@ -2608,22 +2609,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.536876107949066</v>
+        <v>-0.537245532060563</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0575486367539535</v>
+        <v>0.0571166022315857</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.32908472262261</v>
+        <v>-9.40611855520118</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0000142205514383877</v>
+        <v>0.0000133812525769572</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.669583502279045</v>
+        <v>-0.668956652995412</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.404168713619087</v>
+        <v>-0.405534411125715</v>
       </c>
     </row>
     <row r="12">
@@ -2631,22 +2632,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.58310538686948</v>
+        <v>-0.583516920745437</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0587635362310041</v>
+        <v>0.058392380117869</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.92291179647948</v>
+        <v>-9.99303196012166</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00000899277822499477</v>
+        <v>0.00000853246824660668</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.718614344417395</v>
+        <v>-0.718169990761657</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.447596429321564</v>
+        <v>-0.448863850729218</v>
       </c>
     </row>
     <row r="13">
@@ -2654,22 +2655,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.719334442257415</v>
+        <v>-0.719432653971141</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0422525461555415</v>
+        <v>0.0416293471138812</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.0246412987605</v>
+        <v>-17.2818625284481</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000000143884964331902</v>
+        <v>0.000000127984285110272</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.816768988414999</v>
+        <v>-0.815430100561601</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.621899896099832</v>
+        <v>-0.623435207380681</v>
       </c>
     </row>
     <row r="14">
@@ -2677,22 +2678,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.02112971915193</v>
+        <v>-1.02015043314675</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0788926118034798</v>
+        <v>0.0782667031181027</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.9432870304199</v>
+        <v>-13.0342839611803</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0000012019897107447</v>
+        <v>0.00000113907557310498</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.20305640820781</v>
+        <v>-1.20063377418589</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.839203030096049</v>
+        <v>-0.839667092107604</v>
       </c>
     </row>
     <row r="15">
@@ -2700,22 +2701,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.810694155017496</v>
+        <v>-0.811042237269816</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0844182887270715</v>
+        <v>0.0837977292174688</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.60330003417281</v>
+        <v>-9.67857058709823</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0000114736653996938</v>
+        <v>0.0000108271425060334</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.00536307790898</v>
+        <v>-1.00428014736602</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.61602523212601</v>
+        <v>-0.617804327173614</v>
       </c>
     </row>
     <row r="16">
@@ -2723,22 +2724,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.38952873893522</v>
+        <v>-1.3890703225214</v>
       </c>
       <c r="C16" t="n">
-        <v>0.13043525273014</v>
+        <v>0.129095101058301</v>
       </c>
       <c r="D16" t="n">
-        <v>-10.6530152688863</v>
+        <v>-10.7600544957479</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0000052829338152939</v>
+        <v>0.00000489983685934493</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.69031297110733</v>
+        <v>-1.68676415939644</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.08874450676312</v>
+        <v>-1.09137648564636</v>
       </c>
     </row>
     <row r="17">
@@ -2746,22 +2747,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>-2.16534802677748</v>
+        <v>-2.16437613989434</v>
       </c>
       <c r="C17" t="n">
-        <v>0.34294762410445</v>
+        <v>0.338894940204302</v>
       </c>
       <c r="D17" t="n">
-        <v>-6.31393214177214</v>
+        <v>-6.38656965072879</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000229321197144213</v>
+        <v>0.000212149499354833</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.95618666612079</v>
+        <v>-2.94586927340523</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.37450938743417</v>
+        <v>-1.38288300638345</v>
       </c>
     </row>
     <row r="18">
@@ -2769,22 +2770,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.57671863357525</v>
+        <v>-0.577199122068629</v>
       </c>
       <c r="C18" t="n">
-        <v>0.090740906332097</v>
+        <v>0.0901590597822744</v>
       </c>
       <c r="D18" t="n">
-        <v>-6.3556631390098</v>
+        <v>-6.40200910992761</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000219276026761861</v>
+        <v>0.000208685491288659</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.78596753880924</v>
+        <v>-0.785106286752673</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.367469728341261</v>
+        <v>-0.369291957384584</v>
       </c>
     </row>
     <row r="19">
@@ -2792,22 +2793,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.526990102834865</v>
+        <v>-0.525867621995925</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0665104959441302</v>
+        <v>0.0649194665479292</v>
       </c>
       <c r="D19" t="n">
-        <v>-7.92341261862706</v>
+        <v>-8.10030719534154</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000046796125826874</v>
+        <v>0.0000399175523196864</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.68036358151651</v>
+        <v>-0.675572180310698</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.373616624153221</v>
+        <v>-0.376163063681152</v>
       </c>
     </row>
     <row r="20">
@@ -2815,22 +2816,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.526672293693725</v>
+        <v>-0.526530958625125</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02751511162932</v>
+        <v>0.027194268556694</v>
       </c>
       <c r="D20" t="n">
-        <v>-19.1412014164793</v>
+        <v>-19.3618356576653</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0000000575026314200732</v>
+        <v>0.0000000525565134070385</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.590122254891541</v>
+        <v>-0.589241054370714</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.463222332495909</v>
+        <v>-0.463820862879536</v>
       </c>
     </row>
     <row r="21">
@@ -2838,22 +2839,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.52529419380527</v>
+        <v>-1.523933342479</v>
       </c>
       <c r="C21" t="n">
-        <v>0.136481760859964</v>
+        <v>0.134629648902359</v>
       </c>
       <c r="D21" t="n">
-        <v>-11.1758097506544</v>
+        <v>-11.3194482411837</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00000368018231463867</v>
+        <v>0.00000334100331600877</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.84002169872829</v>
+        <v>-1.83438986956892</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.21056668888224</v>
+        <v>-1.21347681538907</v>
       </c>
     </row>
     <row r="22">
@@ -2861,22 +2862,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.835847001506377</v>
+        <v>-0.835740234061319</v>
       </c>
       <c r="C22" t="n">
-        <v>0.425353850700325</v>
+        <v>0.420812493020763</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.96506273572038</v>
+        <v>-1.98601573841603</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0849901566201877</v>
+        <v>0.0822789902627701</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.81671474014634</v>
+        <v>-1.80613558311277</v>
       </c>
       <c r="G22" t="n">
-        <v>0.145020737133588</v>
+        <v>0.134655114990135</v>
       </c>
     </row>
     <row r="23">
@@ -2884,22 +2885,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.59785071885406</v>
+        <v>-1.59650251074948</v>
       </c>
       <c r="C23" t="n">
-        <v>0.137277397949917</v>
+        <v>0.135446816015248</v>
       </c>
       <c r="D23" t="n">
-        <v>-11.6395760898455</v>
+        <v>-11.7869327439174</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00000270382841401389</v>
+        <v>0.0000024571947586216</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.91441296619663</v>
+        <v>-1.90884342858088</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.28128847151148</v>
+        <v>-1.28416159291808</v>
       </c>
     </row>
     <row r="24">
@@ -2907,22 +2908,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.39653251395366</v>
+        <v>-1.39603547577939</v>
       </c>
       <c r="C24" t="n">
-        <v>0.111146558116392</v>
+        <v>0.110047658728097</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.5647841698455</v>
+        <v>-12.6857353615189</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00000150890504913905</v>
+        <v>0.00000140219966437758</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.65283693658377</v>
+        <v>-1.64980583187592</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.14022809132355</v>
+        <v>-1.14226511968286</v>
       </c>
     </row>
     <row r="25">
@@ -2930,22 +2931,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>-1.17773223897253</v>
+        <v>-1.17708894773116</v>
       </c>
       <c r="C25" t="n">
-        <v>0.108115699475087</v>
+        <v>0.106853871931826</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.8932582843245</v>
+        <v>-11.0158754797595</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00000446576434070282</v>
+        <v>0.00000410389320078773</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.42704748904258</v>
+        <v>-1.42349441826852</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.928416988902493</v>
+        <v>-0.930683477193791</v>
       </c>
     </row>
     <row r="26">
@@ -2953,22 +2954,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.475808095365353</v>
+        <v>-0.476457650630253</v>
       </c>
       <c r="C26" t="n">
-        <v>0.103271268120179</v>
+        <v>0.102224608281866</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.60736179603841</v>
+        <v>-4.66088996219488</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00173864613071496</v>
+        <v>0.00162157464617744</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.713952066698264</v>
+        <v>-0.712188020047862</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.237664124032441</v>
+        <v>-0.240727281212644</v>
       </c>
     </row>
     <row r="27">
@@ -2976,22 +2977,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.927545745179019</v>
+        <v>-0.92744652744319</v>
       </c>
       <c r="C27" t="n">
-        <v>0.153022257376905</v>
+        <v>0.151451796367186</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.06150870519708</v>
+        <v>-6.12370767260266</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000302040483792354</v>
+        <v>0.000282016609392226</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.28041570346844</v>
+        <v>-1.27669499615002</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5746757868896</v>
+        <v>-0.578198058736361</v>
       </c>
     </row>
     <row r="28">
@@ -2999,22 +3000,22 @@
         <v>34</v>
       </c>
       <c r="B28" t="n">
-        <v>0.387365944482442</v>
+        <v>0.375760979950115</v>
       </c>
       <c r="C28" t="n">
-        <v>0.239024432495377</v>
+        <v>0.236311519523463</v>
       </c>
       <c r="D28" t="n">
-        <v>1.62061233840576</v>
+        <v>1.59010860201763</v>
       </c>
       <c r="E28" t="n">
-        <v>0.143759544806778</v>
+        <v>0.150474145292783</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.163825385266726</v>
+        <v>-0.16917436126737</v>
       </c>
       <c r="G28" t="n">
-        <v>0.93855727423161</v>
+        <v>0.9206963211676</v>
       </c>
     </row>
     <row r="29">
@@ -3022,22 +3023,22 @@
         <v>35</v>
       </c>
       <c r="B29" t="n">
-        <v>1.61847997347001</v>
+        <v>1.61723552220318</v>
       </c>
       <c r="C29" t="n">
-        <v>0.343392524292571</v>
+        <v>0.33998061670317</v>
       </c>
       <c r="D29" t="n">
-        <v>4.71320677933881</v>
+        <v>4.75684625166485</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00151538873014888</v>
+        <v>0.0014325920488052</v>
       </c>
       <c r="F29" t="n">
-        <v>0.826615392453147</v>
+        <v>0.833238814196407</v>
       </c>
       <c r="G29" t="n">
-        <v>2.41034455448688</v>
+        <v>2.40123223020995</v>
       </c>
     </row>
     <row r="30">
@@ -3045,22 +3046,654 @@
         <v>36</v>
       </c>
       <c r="B30" t="n">
-        <v>0.00230114558426336</v>
+        <v>0.00223367799089</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00286477062597288</v>
+        <v>0.00282433224740537</v>
       </c>
       <c r="D30" t="n">
-        <v>0.803256485318748</v>
+        <v>0.790869414510994</v>
       </c>
       <c r="E30" t="n">
-        <v>0.445034418016337</v>
+        <v>0.451826853584934</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.00430502732564152</v>
+        <v>-0.00427924385081725</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00890731849416825</v>
+        <v>0.00874659983259725</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.686029434169956</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0798098701190026</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-8.59579690014573</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0000124142161754139</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.866571903521652</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.50548696481826</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.740152307594946</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0934458302343421</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-7.92065633895919</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0000239674589037265</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.951541461793188</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.528763153396704</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-2.02464139941014</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.158143747666517</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-12.8025383822291</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.000000442790624923255</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-2.3823874109457</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.66689538787457</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-1.7922398739029</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.129877514763851</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-13.7994623408188</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.000000232294524132862</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-2.08604322421238</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1.49843652359343</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-1.039658019165</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.096170485001297</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-10.8105726944289</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.00000186361446943066</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1.25721077066046</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.822105267669541</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-1.27469665541755</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0646928939021707</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-19.7038125600806</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0000000103561023476017</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.42104214874049</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.12835116209461</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-1.18399855662465</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.132294344829942</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-8.9497291675364</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.00000893817583735658</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.48326915637939</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.884727956869898</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-1.58493968326689</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.143651997774851</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-11.0331892895148</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.00000156953857365484</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.90990307898354</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1.25997628755024</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-1.89384192308325</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.232368347253376</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-8.15017167987253</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0000190728428166605</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-2.41949564423006</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.36818820193645</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.734600687282701</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0851558616409156</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-8.62654282544116</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0000120597694786869</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.927236629647951</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.541964744917451</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.818995523351293</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.100068305594919</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-8.18436485440875</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0000184426439598111</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.04536575762192</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.592625289080666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-1.0032447513567</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.102964560792717</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-9.7435927821455</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.00000443999029513292</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.23616677006832</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.770322732645085</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-1.25196283969623</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0893130279852275</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-14.0176956031913</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.000000202856663271151</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.4540029456842</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1.04992273370825</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-1.06253183574225</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.138619623833556</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-7.66508959090857</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.000031098549754227</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.37611121070172</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.748952460782781</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-1.6490114367041</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.145457101400089</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-11.336754416468</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.00000124785382397481</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.97805826051618</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.31996461289203</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-2.31060822109347</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.2973060817013</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-7.77181619653148</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0000278711289819618</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-2.98316130335754</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.63805513882941</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.630390297328473</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0677227527505679</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-9.30839742516502</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.00000647588895322576</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.783589807547582</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.477190787109364</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.499174091757858</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0486949866583752</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-10.2510366264163</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.00000290990431933859</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.609329804619465</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.389018378896252</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.672467609264481</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0469250089661076</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-14.3306868571977</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.000000167587992240232</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.778619354411531</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.566315864117431</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-1.80577643018178</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.164079363854857</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-11.0055060414493</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.00000160315255401831</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-2.17694973839342</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.43460312197014</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-1.07666421305332</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.36218420194769</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-2.97269789036471</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0156337954032907</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-1.89598179974164</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.257346626365004</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="n">
+        <v>-1.84892772313713</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.156982879790391</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-11.7778940328135</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.000000902669777709799</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-2.20404766909166</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.49380777718261</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" t="n">
+        <v>-1.65382092616869</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.124923449723499</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-13.238674803083</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.000000332100814275087</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.93641740276216</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.37122444957522</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="n">
+        <v>-1.4170496102577</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.14744156491169</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-9.61092356220206</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.000004973830965197</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.75058560241686</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.08351361809855</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.645195741987445</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0857472336017314</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-7.52439134053203</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0000359954951536062</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.839169460669732</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.451222023305157</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" t="n">
+        <v>-1.10434389002018</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.165718738377003</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-6.66396510639522</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0000922529078918</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.4792257210496</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.729462058990765</v>
       </c>
     </row>
   </sheetData>
